--- a/backend/wp_templates/D/D2-6至D2-13  应收账款 -检查（Leap应对措施-检查）.xlsx
+++ b/backend/wp_templates/D/D2-6至D2-13  应收账款 -检查（Leap应对措施-检查）.xlsx
@@ -19353,7 +19353,7 @@
       </c>
       <c r="E14" s="170"/>
       <c r="F14" s="171">
-        <f t="shared" ref="F14:F18" si="1">B14-E14</f>
+        <f t="shared" ref="F14:F18" si="1">D14-E14</f>
         <v>0</v>
       </c>
       <c r="G14" s="172"/>
@@ -19432,11 +19432,11 @@
         <v>0</v>
       </c>
       <c r="C19" s="175">
-        <f>SUM(C14:C18)</f>
+        <f>IF(B19=0,"",D19/B19)</f>
         <v>0</v>
       </c>
       <c r="D19" s="176" t="str">
-        <f>IF(B19=0,"",C19/B19)</f>
+        <f>SUM(D14:D18)</f>
         <v/>
       </c>
       <c r="E19" s="175">
@@ -21652,7 +21652,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="C90" s="142">
-        <f>G70</f>
+        <f>G69</f>
         <v>0</v>
       </c>
       <c r="D90" s="147" t="e">
